--- a/data/personalia/LRT PG.xlsx
+++ b/data/personalia/LRT PG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216ACD14-5FC3-4F12-A395-0155D97EF5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE619F25-E8DC-4D22-BAE7-CDF78C9BC4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="182">
   <si>
     <t>Wilayah</t>
   </si>
@@ -139,15 +148,141 @@
     <t>Assistant Manager</t>
   </si>
   <si>
+    <t>Kantor</t>
+  </si>
+  <si>
     <t>NIPP</t>
   </si>
   <si>
+    <t>Quality Controller</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor</t>
+  </si>
+  <si>
     <t>Kaur UPT Resor</t>
   </si>
   <si>
     <t>Petugas Negative Check</t>
   </si>
   <si>
+    <t>Kepala UPT Workshop</t>
+  </si>
+  <si>
+    <t>Kaur UPT Workshop</t>
+  </si>
+  <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>VACANT</t>
+  </si>
+  <si>
     <t>LRT PG</t>
   </si>
   <si>
@@ -160,6 +295,9 @@
     <t>III.9 Llg</t>
   </si>
   <si>
+    <t>PRP.160791.128383</t>
+  </si>
+  <si>
     <t>ACHMAD SUPRIYADI</t>
   </si>
   <si>
@@ -175,102 +313,147 @@
     <t>AM Power System LRT Pg</t>
   </si>
   <si>
+    <t>PMP.221191.72147</t>
+  </si>
+  <si>
     <t>M MARIO BIMO</t>
   </si>
   <si>
-    <t>Subunit of Field Service Power System 1</t>
-  </si>
-  <si>
     <t>Supervisor Field Service Power System 1</t>
   </si>
   <si>
+    <t>PRP.290387.125860</t>
+  </si>
+  <si>
     <t>PRIMA HARY VALENDO</t>
   </si>
   <si>
     <t>PNC Field Service Power System 1 DIVRE III</t>
   </si>
   <si>
+    <t>PRP.050497.122301</t>
+  </si>
+  <si>
     <t>SUBERTA SATRIA TAMA</t>
   </si>
   <si>
+    <t>PRP.081095.02293</t>
+  </si>
+  <si>
     <t>ADE TRI RAMDANI</t>
   </si>
   <si>
+    <t>PRP.100296.122284</t>
+  </si>
+  <si>
     <t>DEVRI ANGGARA</t>
   </si>
   <si>
+    <t>PRP.010696.122292</t>
+  </si>
+  <si>
     <t>M AGUNG NUGROHO</t>
   </si>
   <si>
+    <t>PRP.081295.122295</t>
+  </si>
+  <si>
     <t>YOSEP RIZALNI SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.300996.122309</t>
+  </si>
+  <si>
     <t>PERMANA KESUMA</t>
   </si>
   <si>
+    <t>PRP.290195.122300</t>
+  </si>
+  <si>
     <t>MAYTA DINATTA (STL)</t>
   </si>
   <si>
-    <t>Subunit of Field Service Power System 2</t>
-  </si>
-  <si>
     <t>Supervisor Field Service Power System 2</t>
   </si>
   <si>
+    <t>PRP.26051990.38313</t>
+  </si>
+  <si>
     <t>YOSUA TRISMADI PUTRA</t>
   </si>
   <si>
     <t>PNC Field Service Power System 2 DIVRE III</t>
   </si>
   <si>
+    <t>PRP.111286.02290</t>
+  </si>
+  <si>
     <t>TOMI ARISCA</t>
   </si>
   <si>
+    <t>PRP.050796.02292</t>
+  </si>
+  <si>
     <t>RAHMAT RAMADHAN</t>
   </si>
   <si>
+    <t>PRP.270293.122302</t>
+  </si>
+  <si>
     <t>YAYANSYAH</t>
   </si>
   <si>
+    <t>PRP.151091.02291</t>
+  </si>
+  <si>
     <t>MUHAMMAD IMADUDDIN</t>
   </si>
   <si>
+    <t>PRP.210798.122297</t>
+  </si>
+  <si>
     <t>RIZKI AKBAR</t>
   </si>
   <si>
+    <t>PRP.300498.122050</t>
+  </si>
+  <si>
     <t>MUHAMMAD REZA RAMADAN</t>
   </si>
   <si>
+    <t>PRP.240197.122298</t>
+  </si>
+  <si>
     <t>ANANTA WIDYA SASMITA</t>
   </si>
   <si>
-    <t>Subunit of Workshop Power System And OCC Power</t>
-  </si>
-  <si>
     <t>Supervisor Workshop Power System And OCC Power</t>
   </si>
   <si>
+    <t>PRP.080587.128179</t>
+  </si>
+  <si>
     <t>M. ADE KURNIAWAN</t>
   </si>
   <si>
     <t>PNC Workshop Power System And OCC Power DIVRE III</t>
   </si>
   <si>
+    <t>PRP.260795.122296</t>
+  </si>
+  <si>
     <t>ALFAIRUS KIBRAN</t>
   </si>
   <si>
+    <t>PRP.080695.122288</t>
+  </si>
+  <si>
     <t>MOHAMMAD ANNAHAL</t>
   </si>
   <si>
     <t>AM Signalling and Communication LRT Pg</t>
   </si>
   <si>
-    <t>VACANT</t>
-  </si>
-  <si>
-    <t>Subunit of Field Service Signalling And Communication 2</t>
-  </si>
-  <si>
     <t>Supervisor Field Service Signalling And Communication 2</t>
   </si>
   <si>
@@ -280,184 +463,127 @@
     <t>PNC Field Service Signalling And Communication 1 DIVRE III</t>
   </si>
   <si>
+    <t>PRP.310795.39902</t>
+  </si>
+  <si>
     <t>OKTAR WIBOWO</t>
   </si>
   <si>
+    <t>PRP.271096.46665</t>
+  </si>
+  <si>
     <t>PANJI EKO PRABOWO</t>
   </si>
   <si>
+    <t>PRP.281096.41550</t>
+  </si>
+  <si>
     <t>FIRMANSYAH</t>
   </si>
   <si>
+    <t>PRP.250896.122045</t>
+  </si>
+  <si>
     <t>HERMAWAN</t>
   </si>
   <si>
+    <t>PRP.150595.122047</t>
+  </si>
+  <si>
     <t>REDDO MANDALA SAPUTRA</t>
   </si>
   <si>
+    <t>PRP.230493.122307</t>
+  </si>
+  <si>
     <t>ESRA FERDINANDUS SIHITE</t>
   </si>
   <si>
+    <t>PRP.170791.39900</t>
+  </si>
+  <si>
     <t>ANDI KUSUMA WIJAYA</t>
   </si>
   <si>
     <t>PNC Field Service Signalling And Communication 2 DIVRE III</t>
   </si>
   <si>
+    <t>PRP.100195.42110</t>
+  </si>
+  <si>
+    <t>PRP.230393.42111</t>
+  </si>
+  <si>
     <t>YUSMANTO</t>
   </si>
   <si>
+    <t>PRP.030396.42112</t>
+  </si>
+  <si>
     <t>AIDIL SAPUTRA</t>
   </si>
   <si>
+    <t>PRP.190296.122285</t>
+  </si>
+  <si>
     <t>RACHMAD WIDIYANTO</t>
   </si>
   <si>
+    <t>PRP.060796.122046</t>
+  </si>
+  <si>
     <t>RANGGA DWI SYAPUTRA</t>
   </si>
   <si>
+    <t>PRP.100399.122049</t>
+  </si>
+  <si>
     <t>EKO SUPRIYADI</t>
   </si>
   <si>
+    <t>PRP.240795.122044</t>
+  </si>
+  <si>
     <t>KUKUH WEBISONO</t>
   </si>
   <si>
+    <t>PRP.050795.122294</t>
+  </si>
+  <si>
     <t>APRIYANDI</t>
   </si>
   <si>
+    <t>PRP.160496.122289</t>
+  </si>
+  <si>
     <t>VONI KATRINA</t>
   </si>
   <si>
-    <t>Subunit of Workshop And OCC Signalling and Communication</t>
-  </si>
-  <si>
     <t>Supervisor Workshop And OCC Signalling and Communication</t>
   </si>
   <si>
+    <t>PRP.180889.128626</t>
+  </si>
+  <si>
     <t>ADI TIRTA</t>
   </si>
   <si>
     <t>PNC Workshop And OCC Signalling and Communication DIVRE III</t>
   </si>
   <si>
+    <t>PRP.201293.122689</t>
+  </si>
+  <si>
     <t>ARIF SAYFURROHIM</t>
   </si>
   <si>
+    <t>PRP.250495.122290</t>
+  </si>
+  <si>
     <t>DEDY CHANDRA</t>
   </si>
   <si>
-    <t>PRP.160791.128383</t>
-  </si>
-  <si>
-    <t>PRP.221191.128461</t>
-  </si>
-  <si>
-    <t>PRP.290387.125860</t>
-  </si>
-  <si>
-    <t>PRP.050497.122301</t>
-  </si>
-  <si>
-    <t>PRP.081095.02293</t>
-  </si>
-  <si>
-    <t>PRP.100296.122284</t>
-  </si>
-  <si>
-    <t>PRP.010696.122292</t>
-  </si>
-  <si>
-    <t>PRP.081295.122295</t>
-  </si>
-  <si>
-    <t>PRP.300996.122309</t>
-  </si>
-  <si>
-    <t>PRP.290195.122300</t>
-  </si>
-  <si>
-    <t>PRP.111286.02290</t>
-  </si>
-  <si>
-    <t>PRP.050796.02292</t>
-  </si>
-  <si>
-    <t>PRP.270293.122302</t>
-  </si>
-  <si>
-    <t>PRP.151091.02291</t>
-  </si>
-  <si>
-    <t>PRP.210798.122297</t>
-  </si>
-  <si>
-    <t>PRP.300498.122050</t>
-  </si>
-  <si>
-    <t>PRP.240197.122298</t>
-  </si>
-  <si>
-    <t>PRP.260795.122296</t>
-  </si>
-  <si>
-    <t>PRP.080695.122288</t>
-  </si>
-  <si>
-    <t>PRP.310795.39902</t>
-  </si>
-  <si>
-    <t>PRP.271096.46665</t>
-  </si>
-  <si>
-    <t>PRP.281096.41550</t>
-  </si>
-  <si>
-    <t>PRP.250896.122045</t>
-  </si>
-  <si>
-    <t>PRP.150595.122047</t>
-  </si>
-  <si>
-    <t>PRP.230493.122307</t>
-  </si>
-  <si>
-    <t>PRP.100195.42110</t>
-  </si>
-  <si>
-    <t>PRP.230393.42111</t>
-  </si>
-  <si>
-    <t>PRP.030396.42112</t>
-  </si>
-  <si>
-    <t>PRP.190296.122285</t>
-  </si>
-  <si>
-    <t>PRP.060796.122046</t>
-  </si>
-  <si>
-    <t>PRP.100399.122049</t>
-  </si>
-  <si>
-    <t>PRP.240795.122044</t>
-  </si>
-  <si>
-    <t>PRP.050795.122294</t>
-  </si>
-  <si>
-    <t>PRP.160496.122289</t>
-  </si>
-  <si>
-    <t>PRP.201293.122689</t>
-  </si>
-  <si>
-    <t>PRP.250495.122290</t>
-  </si>
-  <si>
     <t>PRP.211294.122291</t>
-  </si>
-  <si>
-    <t>PMP.221191.72147</t>
   </si>
 </sst>
 </file>
@@ -528,9 +654,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -539,8 +662,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,30 +970,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T83"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -889,7 +1014,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -898,19 +1023,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -919,7 +1044,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -931,10 +1056,10 @@
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>64481</v>
@@ -943,15 +1068,15 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6">
+        <v>84</v>
+      </c>
+      <c r="H2" s="5">
         <v>45962</v>
       </c>
       <c r="I2" s="2">
@@ -960,29 +1085,31 @@
       <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>41791</v>
       </c>
-      <c r="L2" s="6">
-        <v>33435</v>
-      </c>
-      <c r="M2" s="6">
+      <c r="L2" s="5">
+        <v>32639</v>
+      </c>
+      <c r="M2" s="5">
         <v>53905</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="O2" s="6">
+        <v>85</v>
+      </c>
+      <c r="O2" s="5">
         <v>47324</v>
       </c>
-      <c r="S2" s="3"/>
+      <c r="P2" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2">
         <v>42207</v>
@@ -993,13 +1120,13 @@
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
+      <c r="F3" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="6">
+        <v>88</v>
+      </c>
+      <c r="H3" s="5">
         <v>45519</v>
       </c>
       <c r="I3" s="2">
@@ -1008,23 +1135,22 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>34669</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>25689</v>
       </c>
-      <c r="M3" s="6">
-        <v>46174</v>
-      </c>
-      <c r="S3" s="3"/>
+      <c r="M3" s="5">
+        <v>45809</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2">
         <v>62970</v>
@@ -1035,13 +1161,13 @@
       <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>47</v>
+      <c r="F4" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="6">
+        <v>88</v>
+      </c>
+      <c r="H4" s="5">
         <v>45096</v>
       </c>
       <c r="I4" s="2">
@@ -1050,35 +1176,31 @@
       <c r="J4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>41456</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>33564</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>54027</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45765</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="R4" s="6">
+        <v>91</v>
+      </c>
+      <c r="R4" s="5">
         <v>47285</v>
       </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2">
         <v>64468</v>
@@ -1087,16 +1209,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>50</v>
+        <v>73</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44440</v>
       </c>
       <c r="I5" s="2">
         <v>8</v>
@@ -1104,29 +1226,31 @@
       <c r="J5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>41791</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>31865</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>52322</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="O5" s="6">
+        <v>94</v>
+      </c>
+      <c r="O5" s="5">
         <v>47265</v>
       </c>
-      <c r="S5" s="3"/>
+      <c r="P5" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="C6" s="2">
         <v>66933</v>
@@ -1135,16 +1259,16 @@
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H6" s="5">
+        <v>43221</v>
       </c>
       <c r="I6" s="2">
         <v>5</v>
@@ -1152,29 +1276,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="K6" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L6" s="5">
         <v>35554</v>
       </c>
-      <c r="M6" s="6">
-        <v>56036</v>
+      <c r="M6" s="5">
+        <v>56005</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O6" s="6">
+        <v>97</v>
+      </c>
+      <c r="O6" s="5">
         <v>46837</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="P6" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2">
         <v>66999</v>
@@ -1183,16 +1309,16 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H7" s="5">
+        <v>43221</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
@@ -1200,29 +1326,31 @@
       <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="K7" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L7" s="5">
         <v>34921</v>
       </c>
-      <c r="M7" s="6">
-        <v>55397</v>
+      <c r="M7" s="5">
+        <v>55458</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="O7" s="6">
+        <v>99</v>
+      </c>
+      <c r="O7" s="5">
         <v>46476</v>
       </c>
-      <c r="S7" s="3"/>
+      <c r="P7" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2">
         <v>72309</v>
@@ -1231,16 +1359,16 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H8" s="5">
+        <v>43798</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
@@ -1248,29 +1376,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
-        <v>43137</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L8" s="5">
         <v>35340</v>
       </c>
-      <c r="M8" s="6">
-        <v>55824</v>
+      <c r="M8" s="5">
+        <v>55579</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O8" s="6">
+        <v>101</v>
+      </c>
+      <c r="O8" s="5">
         <v>46819</v>
       </c>
-      <c r="S8" s="3"/>
+      <c r="P8" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>72343</v>
@@ -1279,16 +1409,16 @@
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H9" s="5">
+        <v>43798</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -1296,28 +1426,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="K9" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L9" s="5">
         <v>35070</v>
       </c>
-      <c r="M9" s="6">
-        <v>55550</v>
+      <c r="M9" s="5">
+        <v>55701</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" s="6">
+        <v>103</v>
+      </c>
+      <c r="O9" s="5">
         <v>46727</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2">
         <v>72386</v>
@@ -1326,16 +1459,16 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H10" s="5">
+        <v>43798</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
@@ -1343,29 +1476,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L10" s="5">
         <v>34923</v>
       </c>
-      <c r="M10" s="6">
-        <v>55397</v>
+      <c r="M10" s="5">
+        <v>55519</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="O10" s="6">
+        <v>105</v>
+      </c>
+      <c r="O10" s="5">
         <v>46727</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2">
         <v>72483</v>
@@ -1374,16 +1509,16 @@
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H11" s="5">
+        <v>43798</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
@@ -1391,29 +1526,31 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L11" s="5">
         <v>35338</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>55793</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="O11" s="6">
+        <v>107</v>
+      </c>
+      <c r="O11" s="5">
         <v>46819</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="P11" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2">
         <v>72431</v>
@@ -1422,16 +1559,16 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H12" s="5">
+        <v>43850</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
@@ -1439,29 +1576,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L12" s="5">
         <v>34728</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>55185</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="O12" s="6">
+        <v>109</v>
+      </c>
+      <c r="O12" s="5">
         <v>46819</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="P12" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2">
         <v>67442</v>
@@ -1470,16 +1609,16 @@
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H13" s="5">
+        <v>44440</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
@@ -1487,23 +1626,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>42248</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>33019</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>53479</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="N13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="O13" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>66830</v>
@@ -1512,16 +1659,16 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H14" s="5">
+        <v>43221</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
@@ -1529,29 +1676,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="K14" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L14" s="5">
         <v>31728</v>
       </c>
-      <c r="M14" s="6">
-        <v>52201</v>
+      <c r="M14" s="5">
+        <v>52232</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="5">
         <v>46476</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="P14" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C15" s="2">
         <v>66927</v>
@@ -1560,16 +1709,16 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H15" s="5">
+        <v>43221</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
@@ -1577,29 +1726,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="K15" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L15" s="5">
         <v>35192</v>
       </c>
-      <c r="M15" s="6">
-        <v>55671</v>
+      <c r="M15" s="5">
+        <v>55732</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="O15" s="6">
+        <v>117</v>
+      </c>
+      <c r="O15" s="5">
         <v>46476</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="P15" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2">
         <v>69076</v>
@@ -1608,16 +1759,16 @@
         <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H16" s="5">
+        <v>43221</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
@@ -1625,28 +1776,31 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="K16" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L16" s="5">
         <v>34027</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>54483</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="O16" s="6">
+        <v>119</v>
+      </c>
+      <c r="O16" s="5">
         <v>46837</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P16" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C17" s="2">
         <v>67000</v>
@@ -1655,16 +1809,16 @@
         <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H17" s="5">
+        <v>43221</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
@@ -1672,29 +1826,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="K17" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L17" s="5">
         <v>33526</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>53997</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="O17" s="6">
+        <v>121</v>
+      </c>
+      <c r="O17" s="5">
         <v>46305</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P17" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="C18" s="2">
         <v>72413</v>
@@ -1703,16 +1859,16 @@
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H18" s="5">
+        <v>43798</v>
       </c>
       <c r="I18" s="2">
         <v>5</v>
@@ -1720,29 +1876,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L18" s="6">
+      <c r="K18" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L18" s="5">
         <v>35997</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>56462</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="O18" s="6">
+        <v>123</v>
+      </c>
+      <c r="O18" s="5">
         <v>46744</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P18" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C19" s="2">
         <v>72457</v>
@@ -1751,16 +1909,16 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H19" s="5">
+        <v>44729</v>
       </c>
       <c r="I19" s="2">
         <v>5</v>
@@ -1768,29 +1926,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="K19" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L19" s="5">
         <v>35915</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>56370</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O19" s="6">
+        <v>125</v>
+      </c>
+      <c r="O19" s="5">
         <v>46837</v>
       </c>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P19" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="C20" s="2">
         <v>72417</v>
@@ -1799,16 +1959,16 @@
         <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H20" s="5">
+        <v>43850</v>
       </c>
       <c r="I20" s="2">
         <v>5</v>
@@ -1816,29 +1976,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="K20" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L20" s="5">
         <v>35454</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>55916</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="O20" s="6">
+        <v>127</v>
+      </c>
+      <c r="O20" s="5">
         <v>46861</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2">
         <v>57335</v>
@@ -1847,16 +2009,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H21" s="5">
+        <v>44440</v>
       </c>
       <c r="I21" s="2">
         <v>8</v>
@@ -1864,23 +2026,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>40163</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>31905</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>52383</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="C22" s="2">
         <v>72394</v>
@@ -1889,16 +2059,16 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>74</v>
+        <v>41</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H22" s="5">
+        <v>43798</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
@@ -1906,29 +2076,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="K22" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L22" s="5">
         <v>34906</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>55366</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O22" s="6">
+        <v>133</v>
+      </c>
+      <c r="O22" s="5">
         <v>46727</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P22" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="C23" s="2">
         <v>72319</v>
@@ -1937,16 +2109,16 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>74</v>
+        <v>41</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H23" s="5">
+        <v>43850</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -1954,29 +2126,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="K23" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L23" s="5">
         <v>34917</v>
       </c>
-      <c r="M23" s="6">
-        <v>55397</v>
+      <c r="M23" s="5">
+        <v>55335</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="O23" s="6">
+        <v>135</v>
+      </c>
+      <c r="O23" s="5">
         <v>46819</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2">
         <v>64521</v>
@@ -1987,14 +2161,14 @@
       <c r="E24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>77</v>
+      <c r="F24" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H24" s="5">
+        <v>44886</v>
       </c>
       <c r="I24" s="2">
         <v>9</v>
@@ -2002,43 +2176,42 @@
       <c r="J24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>41791</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>32013</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>52475</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="C26" s="2">
         <v>66928</v>
@@ -2047,16 +2220,16 @@
         <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H26" s="5">
+        <v>43221</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
@@ -2064,29 +2237,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="K26" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L26" s="5">
         <v>34911</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>55366</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O26" s="6">
+        <v>141</v>
+      </c>
+      <c r="O26" s="5">
         <v>46446</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P26" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2">
         <v>66825</v>
@@ -2095,16 +2270,16 @@
         <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H27" s="5">
+        <v>43221</v>
       </c>
       <c r="I27" s="2">
         <v>5</v>
@@ -2112,29 +2287,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="K27" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L27" s="5">
         <v>35365</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>55824</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O27" s="6">
+        <v>143</v>
+      </c>
+      <c r="O27" s="5">
         <v>46595</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P27" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="C28" s="2">
         <v>66829</v>
@@ -2143,16 +2320,16 @@
         <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H28" s="5">
+        <v>43221</v>
       </c>
       <c r="I28" s="2">
         <v>5</v>
@@ -2160,29 +2337,31 @@
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L28" s="6">
+      <c r="K28" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L28" s="5">
         <v>35366</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>55824</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="O28" s="6">
+        <v>145</v>
+      </c>
+      <c r="O28" s="5">
         <v>46476</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2">
         <v>72359</v>
@@ -2191,16 +2370,16 @@
         <v>33</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H29" s="5">
+        <v>43798</v>
       </c>
       <c r="I29" s="2">
         <v>5</v>
@@ -2208,29 +2387,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="K29" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L29" s="5">
         <v>35302</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>55763</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="O29" s="6">
+        <v>147</v>
+      </c>
+      <c r="O29" s="5">
         <v>46744</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="C30" s="2">
         <v>72370</v>
@@ -2239,16 +2420,16 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H30" s="5">
+        <v>43833</v>
       </c>
       <c r="I30" s="2">
         <v>5</v>
@@ -2256,28 +2437,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="K30" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L30" s="5">
         <v>34834</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>55305</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="O30" s="6">
+        <v>149</v>
+      </c>
+      <c r="O30" s="5">
         <v>46744</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="C31" s="2">
         <v>72446</v>
@@ -2286,16 +2470,16 @@
         <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H31" s="5">
+        <v>43833</v>
       </c>
       <c r="I31" s="2">
         <v>5</v>
@@ -2303,29 +2487,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L31" s="6">
+      <c r="K31" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L31" s="5">
         <v>34082</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="5">
         <v>54544</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="O31" s="6">
+        <v>151</v>
+      </c>
+      <c r="O31" s="5">
         <v>46744</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="C32" s="2">
         <v>70560</v>
@@ -2334,16 +2520,16 @@
         <v>31</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H32" s="5">
+        <v>44851</v>
       </c>
       <c r="I32" s="2">
         <v>8</v>
@@ -2351,23 +2537,31 @@
       <c r="J32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>42646</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>33436</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>53905</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="O32" s="5">
+        <v>46446</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="C33" s="2">
         <v>66925</v>
@@ -2376,16 +2570,16 @@
         <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H33" s="5">
+        <v>43409</v>
       </c>
       <c r="I33" s="2">
         <v>5</v>
@@ -2393,29 +2587,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L33" s="6">
+      <c r="K33" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L33" s="5">
         <v>34973</v>
       </c>
-      <c r="M33" s="6">
-        <v>55458</v>
+      <c r="M33" s="5">
+        <v>55185</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="O33" s="6">
+        <v>156</v>
+      </c>
+      <c r="O33" s="5">
         <v>46481</v>
       </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P33" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C34" s="2">
         <v>66934</v>
@@ -2424,16 +2620,16 @@
         <v>33</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H34" s="5">
+        <v>43221</v>
       </c>
       <c r="I34" s="2">
         <v>5</v>
@@ -2441,29 +2637,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="K34" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L34" s="5">
         <v>34051</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>54514</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="O34" s="6">
+        <v>157</v>
+      </c>
+      <c r="O34" s="5">
         <v>46481</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P34" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C35" s="2">
         <v>66948</v>
@@ -2472,16 +2670,16 @@
         <v>33</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H35" s="5">
+        <v>43221</v>
       </c>
       <c r="I35" s="2">
         <v>5</v>
@@ -2489,29 +2687,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L35" s="6">
+      <c r="K35" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L35" s="5">
         <v>35127</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>55610</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="O35" s="6">
+        <v>159</v>
+      </c>
+      <c r="O35" s="5">
         <v>46481</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="36" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P35" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="C36" s="2">
         <v>72315</v>
@@ -2520,16 +2720,16 @@
         <v>33</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H36" s="5">
+        <v>43798</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -2537,28 +2737,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L36" s="6">
+      <c r="K36" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L36" s="5">
         <v>35114</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>55579</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="O36" s="6">
+        <v>161</v>
+      </c>
+      <c r="O36" s="5">
         <v>46744</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P36" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="C37" s="2">
         <v>72436</v>
@@ -2567,16 +2770,16 @@
         <v>33</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H37" s="5">
+        <v>43798</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -2584,29 +2787,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="K37" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L37" s="5">
         <v>35223</v>
       </c>
-      <c r="M37" s="6">
-        <v>55701</v>
+      <c r="M37" s="5">
+        <v>55732</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="O37" s="6">
+        <v>163</v>
+      </c>
+      <c r="O37" s="5">
         <v>46837</v>
       </c>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="C38" s="2">
         <v>72445</v>
@@ -2615,16 +2820,16 @@
         <v>33</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H38" s="5">
+        <v>43833</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>
@@ -2632,29 +2837,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L38" s="6">
+      <c r="K38" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L38" s="5">
         <v>36436</v>
       </c>
-      <c r="M38" s="6">
-        <v>56919</v>
+      <c r="M38" s="5">
+        <v>56705</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="O38" s="6">
+        <v>165</v>
+      </c>
+      <c r="O38" s="5">
         <v>46744</v>
       </c>
-      <c r="S38" s="3"/>
-    </row>
-    <row r="39" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="C39" s="2">
         <v>72349</v>
@@ -2663,16 +2870,16 @@
         <v>33</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H39" s="5">
+        <v>43833</v>
       </c>
       <c r="I39" s="2">
         <v>5</v>
@@ -2680,29 +2887,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="K39" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L39" s="5">
         <v>34904</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>55366</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O39" s="6">
+        <v>167</v>
+      </c>
+      <c r="O39" s="5">
         <v>46744</v>
       </c>
-      <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2">
         <v>72383</v>
@@ -2711,16 +2920,16 @@
         <v>33</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H40" s="5">
+        <v>43833</v>
       </c>
       <c r="I40" s="2">
         <v>5</v>
@@ -2728,29 +2937,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L40" s="6">
+      <c r="K40" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L40" s="5">
         <v>34826</v>
       </c>
-      <c r="M40" s="6">
-        <v>55305</v>
+      <c r="M40" s="5">
+        <v>55366</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="O40" s="6">
+        <v>169</v>
+      </c>
+      <c r="O40" s="5">
         <v>46837</v>
       </c>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="C41" s="2">
         <v>72325</v>
@@ -2759,16 +2970,16 @@
         <v>33</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H41" s="5">
+        <v>44046</v>
       </c>
       <c r="I41" s="2">
         <v>5</v>
@@ -2776,29 +2987,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="K41" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L41" s="5">
         <v>35171</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>55640</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="O41" s="6">
+        <v>171</v>
+      </c>
+      <c r="O41" s="5">
         <v>46744</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P41" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C42" s="2">
         <v>61685</v>
@@ -2807,16 +3020,16 @@
         <v>31</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>100</v>
+        <v>77</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H42" s="5">
+        <v>44440</v>
       </c>
       <c r="I42" s="2">
         <v>8</v>
@@ -2824,23 +3037,31 @@
       <c r="J42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <v>41000</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="5">
         <v>32738</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="5">
         <v>53206</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N42" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="O42" s="5">
+        <v>47370</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2">
         <v>72310</v>
@@ -2849,16 +3070,16 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>102</v>
+        <v>41</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H43" s="5">
+        <v>43798</v>
       </c>
       <c r="I43" s="2">
         <v>5</v>
@@ -2866,30 +3087,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L43" s="6">
+      <c r="K43" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L43" s="5">
         <v>34323</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>54789</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="O43" s="6">
+        <v>177</v>
+      </c>
+      <c r="O43" s="5">
         <v>46937</v>
       </c>
-      <c r="P43" s="3"/>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P43" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="C44" s="2">
         <v>72329</v>
@@ -2898,16 +3120,16 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>102</v>
+        <v>41</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H44" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H44" s="5">
+        <v>43833</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
@@ -2915,30 +3137,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L44" s="6">
+      <c r="K44" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L44" s="5">
         <v>34814</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>55274</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="O44" s="6">
+        <v>179</v>
+      </c>
+      <c r="O44" s="5">
         <v>46837</v>
       </c>
-      <c r="P44" s="3"/>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P44" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="C45" s="2">
         <v>72340</v>
@@ -2947,16 +3170,16 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>102</v>
+        <v>41</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="6">
-        <v>44927</v>
+        <v>88</v>
+      </c>
+      <c r="H45" s="5">
+        <v>43833</v>
       </c>
       <c r="I45" s="2">
         <v>5</v>
@@ -2964,230 +3187,222 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L45" s="6">
+      <c r="K45" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L45" s="5">
         <v>34689</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="5">
         <v>55154</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O45" s="6">
+        <v>181</v>
+      </c>
+      <c r="O45" s="5">
         <v>46937</v>
       </c>
-      <c r="P45" s="3"/>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="D46" s="2"/>
-      <c r="P46" s="3"/>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="D47" s="2"/>
-      <c r="P47" s="3"/>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="D48" s="2"/>
-      <c r="P48" s="3"/>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D49" s="2"/>
-      <c r="P49" s="3"/>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D50" s="2"/>
-      <c r="P50" s="3"/>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D51" s="2"/>
-      <c r="P51" s="3"/>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D52" s="2"/>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D53" s="2"/>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D54" s="2"/>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D55" s="2"/>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D56" s="2"/>
-      <c r="P56" s="3"/>
-      <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D57" s="2"/>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D58" s="2"/>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="D59" s="2"/>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="H60" s="8"/>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="H61" s="8"/>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="H63" s="8"/>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="4:19" x14ac:dyDescent="0.45">
-      <c r="H64" s="8"/>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H67" s="8"/>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H68" s="8"/>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H69" s="8"/>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H70" s="8"/>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H71" s="8"/>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H72" s="8"/>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H73" s="8"/>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H74" s="8"/>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="78" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H78" s="8"/>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
-    </row>
-    <row r="79" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H79" s="8"/>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
-    </row>
-    <row r="80" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H80" s="8"/>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
-    </row>
-    <row r="81" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H82" s="8"/>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
-    </row>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="49" x14ac:dyDescent="0.45"/>
+    <row r="50" x14ac:dyDescent="0.45"/>
+    <row r="51" x14ac:dyDescent="0.45"/>
+    <row r="52" x14ac:dyDescent="0.45"/>
+    <row r="53" x14ac:dyDescent="0.45"/>
+    <row r="54" x14ac:dyDescent="0.45"/>
+    <row r="55" x14ac:dyDescent="0.45"/>
+    <row r="56" x14ac:dyDescent="0.45"/>
+    <row r="57" x14ac:dyDescent="0.45"/>
+    <row r="58" x14ac:dyDescent="0.45"/>
+    <row r="59" x14ac:dyDescent="0.45"/>
+    <row r="60" x14ac:dyDescent="0.45"/>
+    <row r="61" x14ac:dyDescent="0.45"/>
+    <row r="62" x14ac:dyDescent="0.45"/>
+    <row r="63" x14ac:dyDescent="0.45"/>
+    <row r="64" x14ac:dyDescent="0.45"/>
+    <row r="65" x14ac:dyDescent="0.45"/>
+    <row r="66" x14ac:dyDescent="0.45"/>
+    <row r="67" x14ac:dyDescent="0.45"/>
+    <row r="68" x14ac:dyDescent="0.45"/>
+    <row r="69" x14ac:dyDescent="0.45"/>
+    <row r="70" x14ac:dyDescent="0.45"/>
+    <row r="71" x14ac:dyDescent="0.45"/>
+    <row r="72" x14ac:dyDescent="0.45"/>
+    <row r="73" x14ac:dyDescent="0.45"/>
+    <row r="74" x14ac:dyDescent="0.45"/>
+    <row r="75" x14ac:dyDescent="0.45"/>
+    <row r="76" x14ac:dyDescent="0.45"/>
+    <row r="77" x14ac:dyDescent="0.45"/>
+    <row r="78" x14ac:dyDescent="0.45"/>
+    <row r="79" x14ac:dyDescent="0.45"/>
+    <row r="80" x14ac:dyDescent="0.45"/>
+    <row r="81" x14ac:dyDescent="0.45"/>
+    <row r="82" x14ac:dyDescent="0.45"/>
+    <row r="83" x14ac:dyDescent="0.45"/>
+    <row r="84" x14ac:dyDescent="0.45"/>
+    <row r="85" x14ac:dyDescent="0.45"/>
+    <row r="86" x14ac:dyDescent="0.45"/>
+    <row r="87" x14ac:dyDescent="0.45"/>
+    <row r="88" x14ac:dyDescent="0.45"/>
+    <row r="89" x14ac:dyDescent="0.45"/>
+    <row r="90" x14ac:dyDescent="0.45"/>
+    <row r="91" x14ac:dyDescent="0.45"/>
+    <row r="92" x14ac:dyDescent="0.45"/>
+    <row r="93" x14ac:dyDescent="0.45"/>
+    <row r="94" x14ac:dyDescent="0.45"/>
+    <row r="95" x14ac:dyDescent="0.45"/>
+    <row r="96" x14ac:dyDescent="0.45"/>
+    <row r="97" x14ac:dyDescent="0.45"/>
+    <row r="98" x14ac:dyDescent="0.45"/>
+    <row r="99" x14ac:dyDescent="0.45"/>
+    <row r="100" x14ac:dyDescent="0.45"/>
+    <row r="101" x14ac:dyDescent="0.45"/>
+    <row r="102" x14ac:dyDescent="0.45"/>
+    <row r="103" x14ac:dyDescent="0.45"/>
+    <row r="104" x14ac:dyDescent="0.45"/>
+    <row r="105" x14ac:dyDescent="0.45"/>
+    <row r="106" x14ac:dyDescent="0.45"/>
+    <row r="107" x14ac:dyDescent="0.45"/>
+    <row r="108" x14ac:dyDescent="0.45"/>
+    <row r="109" x14ac:dyDescent="0.45"/>
+    <row r="110" x14ac:dyDescent="0.45"/>
+    <row r="111" x14ac:dyDescent="0.45"/>
+    <row r="112" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T198" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D985</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J985</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I985</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3197,130 +3412,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
